--- a/02_Literature_Review/Summary/Design_Summary.xlsx
+++ b/02_Literature_Review/Summary/Design_Summary.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jeffm\Desktop\FYP_Lattice_Project\02_Literature_Review\Summary\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{CEDE4E79-5765-49E8-B61F-852415E63D4E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C2AC9488-662D-4405-ACF6-B41883E5006F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{E00CCA49-041F-4014-9FB6-E6CB9BE8062A}"/>
+    <workbookView xWindow="4320" yWindow="1080" windowWidth="15375" windowHeight="7785" xr2:uid="{E00CCA49-041F-4014-9FB6-E6CB9BE8062A}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="16">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="20">
   <si>
     <t>Parameter</t>
   </si>
@@ -98,6 +98,18 @@
   </si>
   <si>
     <t>20 mm (3 * 3 * 3 grid)</t>
+  </si>
+  <si>
+    <t>Volumetric Model 1</t>
+  </si>
+  <si>
+    <t>20mm</t>
+  </si>
+  <si>
+    <t>58,490.481 mm^3</t>
+  </si>
+  <si>
+    <t>29.999 mm, 30.002 mm, 30.00 mm</t>
   </si>
 </sst>
 </file>
@@ -140,7 +152,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -149,12 +161,25 @@
       <diagonal/>
     </border>
     <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
       <left style="medium">
         <color rgb="FFC4C7C5"/>
       </left>
-      <right style="medium">
-        <color rgb="FFC4C7C5"/>
-      </right>
+      <right/>
       <top style="medium">
         <color rgb="FFC4C7C5"/>
       </top>
@@ -167,16 +192,25 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -512,75 +546,98 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9E2399E0-1F0D-4032-A80F-589B819EF1CF}">
-  <dimension ref="A1:B8"/>
+  <dimension ref="A1:C8"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="25.28515625" customWidth="1"/>
     <col min="2" max="2" width="24.42578125" customWidth="1"/>
+    <col min="3" max="3" width="31" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" ht="15.75" thickBot="1">
+    <row r="1" spans="1:3" ht="15.75" thickBot="1">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="2" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="2" spans="1:2" ht="29.25" thickBot="1">
+      <c r="C1" s="3"/>
+    </row>
+    <row r="2" spans="1:3" ht="29.25" thickBot="1">
       <c r="A2" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="B2" s="2" t="s">
+      <c r="B2" s="4" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="3" spans="1:2" ht="15.75" thickBot="1">
+      <c r="C2" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" ht="15.75" thickBot="1">
       <c r="A3" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="B3" s="3" t="s">
+      <c r="B3" s="5" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="4" spans="1:2" ht="15.75" thickBot="1">
+      <c r="C3" s="5" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" ht="15.75" thickBot="1">
       <c r="A4" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="B4" s="3" t="s">
+      <c r="B4" s="5" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="5" spans="1:2" ht="29.25" thickBot="1">
+      <c r="C4" s="3" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" ht="29.25" thickBot="1">
       <c r="A5" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="B5" s="3" t="s">
+      <c r="B5" s="5" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="6" spans="1:2" ht="15.75" thickBot="1">
+      <c r="C5" s="6">
+        <v>202604</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" ht="15.75" thickBot="1">
       <c r="A6" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="B6" s="3" t="s">
+      <c r="B6" s="5" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="7" spans="1:2" ht="29.25" thickBot="1">
+      <c r="C6" s="3">
+        <v>72.528000000000006</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" ht="29.25" thickBot="1">
       <c r="A7" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="B7" s="3" t="s">
+      <c r="B7" s="5" t="s">
         <v>13</v>
       </c>
-    </row>
-    <row r="8" spans="1:2" ht="15.75" thickBot="1">
+      <c r="C7" s="3" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" ht="15.75" thickBot="1">
       <c r="A8" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="B8" s="3" t="s">
+      <c r="B8" s="5" t="s">
         <v>14</v>
+      </c>
+      <c r="C8" s="3" t="s">
+        <v>19</v>
       </c>
     </row>
   </sheetData>
